--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9237DECF-0468-40B0-8DC7-333209CAA2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F66730A-444C-455F-9893-FDBC24891C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="3" activeTab="5" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="3" activeTab="4" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="9">
   <si>
     <t>table</t>
     <phoneticPr fontId="1"/>
@@ -2149,7 +2149,7 @@
         <v>25</v>
       </c>
       <c r="D21">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -2188,7 +2188,7 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D24">
         <v>50</v>
@@ -2555,7 +2555,7 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -6130,10 +6130,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EE32E5-1661-4B26-984C-DC08FEB1184C}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6146,2016 +6146,1404 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
+      <c r="C3">
         <v>30</v>
       </c>
-      <c r="H3">
+      <c r="D3">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
+      <c r="C4">
         <v>44</v>
       </c>
-      <c r="H4">
+      <c r="D4">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
+      <c r="C5">
         <v>69</v>
       </c>
-      <c r="H5">
+      <c r="D5">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
+      <c r="C6">
         <v>19</v>
       </c>
-      <c r="H6">
+      <c r="D6">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
+      <c r="C7">
         <v>57</v>
       </c>
-      <c r="H7">
+      <c r="D7">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8">
+      <c r="C8">
         <v>28</v>
       </c>
-      <c r="H8">
+      <c r="D8">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9">
+      <c r="C9">
         <v>6</v>
       </c>
-      <c r="H9">
+      <c r="D9">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="H10">
+      <c r="D10">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11">
+      <c r="C11">
         <v>12</v>
       </c>
-      <c r="H11">
+      <c r="D11">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-      <c r="G12">
+      <c r="C12">
         <v>59</v>
       </c>
-      <c r="H12">
+      <c r="D12">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
-      <c r="G13">
+      <c r="C13">
         <v>11</v>
       </c>
-      <c r="H13">
+      <c r="D13">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>13</v>
-      </c>
-      <c r="G14">
+      <c r="C14">
         <v>23</v>
       </c>
-      <c r="H14">
+      <c r="D14">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>14</v>
-      </c>
-      <c r="G15">
+      <c r="C15">
         <v>43</v>
       </c>
-      <c r="H15">
+      <c r="D15">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
+      <c r="C16">
         <v>15</v>
       </c>
-      <c r="G16">
-        <v>15</v>
-      </c>
-      <c r="H16">
+      <c r="D16">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>16</v>
-      </c>
-      <c r="G17">
+      <c r="C17">
         <v>70</v>
       </c>
-      <c r="H17">
+      <c r="D17">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>17</v>
-      </c>
-      <c r="G18">
+      <c r="C18">
         <v>54</v>
       </c>
-      <c r="H18">
+      <c r="D18">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>18</v>
-      </c>
-      <c r="G19">
+      <c r="C19">
         <v>8</v>
       </c>
-      <c r="H19">
+      <c r="D19">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>19</v>
-      </c>
-      <c r="G20">
+      <c r="C20">
         <v>39</v>
       </c>
-      <c r="H20">
+      <c r="D20">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>20</v>
-      </c>
-      <c r="G21">
+      <c r="C21">
         <v>25</v>
       </c>
-      <c r="H21">
+      <c r="D21">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>21</v>
-      </c>
-      <c r="G22">
+      <c r="C22">
         <v>10</v>
       </c>
-      <c r="H22">
+      <c r="D22">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>22</v>
-      </c>
-      <c r="G23">
+      <c r="C23">
         <v>20</v>
       </c>
-      <c r="H23">
+      <c r="D23">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>23</v>
-      </c>
-      <c r="G24">
+      <c r="C24">
         <v>7</v>
       </c>
-      <c r="H24">
+      <c r="D24">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>24</v>
-      </c>
-      <c r="G25">
+      <c r="C25">
         <v>2</v>
       </c>
-      <c r="H25">
+      <c r="D25">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="G26">
+      <c r="C26">
         <v>16</v>
       </c>
-      <c r="H26">
+      <c r="D26">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>26</v>
-      </c>
-      <c r="G27">
+      <c r="C27">
         <v>31</v>
       </c>
-      <c r="H27">
+      <c r="D27">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>27</v>
-      </c>
-      <c r="G28">
+      <c r="C28">
         <v>40</v>
       </c>
-      <c r="H28">
+      <c r="D28">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>28</v>
-      </c>
-      <c r="G29">
+      <c r="C29">
         <v>69</v>
       </c>
-      <c r="H29">
+      <c r="D29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>29</v>
-      </c>
-      <c r="G30">
+      <c r="C30">
         <v>45</v>
       </c>
-      <c r="H30">
+      <c r="D30">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>30</v>
-      </c>
-      <c r="G31">
+      <c r="C31">
         <v>22</v>
       </c>
-      <c r="H31">
+      <c r="D31">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <v>31</v>
-      </c>
-      <c r="G32">
+      <c r="C32">
         <v>50</v>
       </c>
-      <c r="H32">
+      <c r="D32">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <v>32</v>
-      </c>
-      <c r="G33">
+      <c r="C33">
         <v>55</v>
       </c>
-      <c r="H33">
+      <c r="D33">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <v>33</v>
-      </c>
-      <c r="G34">
+      <c r="C34">
         <v>38</v>
       </c>
-      <c r="H34">
+      <c r="D34">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>34</v>
-      </c>
-      <c r="G35">
+      <c r="C35">
         <v>4</v>
       </c>
-      <c r="H35">
+      <c r="D35">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>35</v>
-      </c>
-      <c r="G36">
+      <c r="C36">
         <v>49</v>
       </c>
-      <c r="H36">
+      <c r="D36">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>36</v>
-      </c>
-      <c r="G37">
+      <c r="C37">
         <v>18</v>
       </c>
-      <c r="H37">
+      <c r="D37">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>37</v>
-      </c>
-      <c r="G38">
+      <c r="C38">
         <v>48</v>
       </c>
-      <c r="H38">
+      <c r="D38">
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-      <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <v>38</v>
-      </c>
-      <c r="G39">
+      <c r="C39">
         <v>30</v>
       </c>
-      <c r="H39">
+      <c r="D39">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>39</v>
-      </c>
-      <c r="G40">
+      <c r="C40">
         <v>24</v>
       </c>
-      <c r="H40">
+      <c r="D40">
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>40</v>
-      </c>
-      <c r="G41">
+      <c r="C41">
         <v>68</v>
       </c>
-      <c r="H41">
+      <c r="D41">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>41</v>
-      </c>
-      <c r="G42">
+      <c r="C42">
         <v>27</v>
       </c>
-      <c r="H42">
+      <c r="D42">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>42</v>
-      </c>
-      <c r="G43">
+      <c r="C43">
         <v>32</v>
       </c>
-      <c r="H43">
+      <c r="D43">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>43</v>
-      </c>
-      <c r="G44">
+      <c r="C44">
         <v>5</v>
       </c>
-      <c r="H44">
+      <c r="D44">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>44</v>
-      </c>
-      <c r="G45">
+      <c r="C45">
         <v>8</v>
       </c>
-      <c r="H45">
+      <c r="D45">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>45</v>
-      </c>
-      <c r="G46">
+      <c r="C46">
         <v>28</v>
       </c>
-      <c r="H46">
+      <c r="D46">
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
-      <c r="F47">
-        <v>46</v>
-      </c>
-      <c r="G47">
+      <c r="C47">
         <v>33</v>
       </c>
-      <c r="H47">
+      <c r="D47">
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48">
-        <v>47</v>
-      </c>
-      <c r="G48">
+      <c r="C48">
         <v>3</v>
       </c>
-      <c r="H48">
+      <c r="D48">
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49">
-        <v>48</v>
-      </c>
-      <c r="G49">
+      <c r="C49">
         <v>52</v>
       </c>
-      <c r="H49">
+      <c r="D49">
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50">
-        <v>49</v>
-      </c>
-      <c r="G50">
+      <c r="C50">
         <v>58</v>
       </c>
-      <c r="H50">
+      <c r="D50">
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="F51">
-        <v>50</v>
-      </c>
-      <c r="G51">
+      <c r="C51">
         <v>26</v>
       </c>
-      <c r="H51">
+      <c r="D51">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52">
-        <v>51</v>
-      </c>
-      <c r="G52">
+      <c r="C52">
         <v>19</v>
       </c>
-      <c r="H52">
+      <c r="D52">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
-        <v>52</v>
-      </c>
-      <c r="G53">
+      <c r="C53">
         <v>11</v>
       </c>
-      <c r="H53">
+      <c r="D53">
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54">
-        <v>53</v>
-      </c>
-      <c r="G54">
+      <c r="C54">
         <v>15</v>
       </c>
-      <c r="H54">
+      <c r="D54">
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55">
-        <v>54</v>
-      </c>
-      <c r="G55">
+      <c r="C55">
         <v>65</v>
       </c>
-      <c r="H55">
+      <c r="D55">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56">
+      <c r="C56">
         <v>55</v>
       </c>
-      <c r="G56">
-        <v>55</v>
-      </c>
-      <c r="H56">
+      <c r="D56">
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57">
-        <v>56</v>
-      </c>
-      <c r="G57">
+      <c r="C57">
         <v>6</v>
       </c>
-      <c r="H57">
+      <c r="D57">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58">
-        <v>57</v>
-      </c>
-      <c r="G58">
+      <c r="C58">
         <v>10</v>
       </c>
-      <c r="H58">
+      <c r="D58">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59">
-        <v>58</v>
-      </c>
-      <c r="G59">
+      <c r="C59">
         <v>43</v>
       </c>
-      <c r="H59">
+      <c r="D59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60">
-        <v>59</v>
-      </c>
-      <c r="G60">
+      <c r="C60">
         <v>34</v>
       </c>
-      <c r="H60">
+      <c r="D60">
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>60</v>
-      </c>
-      <c r="G61">
+      <c r="C61">
         <v>2</v>
       </c>
-      <c r="H61">
+      <c r="D61">
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62">
-        <v>61</v>
-      </c>
-      <c r="G62">
+      <c r="C62">
         <v>23</v>
       </c>
-      <c r="H62">
+      <c r="D62">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63">
+      <c r="C63">
+        <v>27</v>
+      </c>
+      <c r="D63">
         <v>62</v>
       </c>
-      <c r="G63">
-        <v>27</v>
-      </c>
-      <c r="H63">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64">
-        <v>63</v>
-      </c>
-      <c r="G64">
+      <c r="C64">
         <v>59</v>
       </c>
-      <c r="H64">
+      <c r="D64">
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65">
-        <v>64</v>
-      </c>
-      <c r="G65">
+      <c r="C65">
         <v>16</v>
       </c>
-      <c r="H65">
+      <c r="D65">
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66">
-        <v>65</v>
-      </c>
-      <c r="G66">
+      <c r="C66">
         <v>7</v>
       </c>
-      <c r="H66">
+      <c r="D66">
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>66</v>
-      </c>
-      <c r="G67">
+      <c r="C67">
         <v>20</v>
       </c>
-      <c r="H67">
+      <c r="D67">
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>67</v>
-      </c>
-      <c r="G68">
+      <c r="C68">
         <v>59</v>
       </c>
-      <c r="H68">
+      <c r="D68">
         <v>27</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69">
-        <v>68</v>
-      </c>
-      <c r="G69">
+      <c r="C69">
         <v>69</v>
       </c>
-      <c r="H69">
+      <c r="D69">
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70">
-        <v>69</v>
-      </c>
-      <c r="G70">
+      <c r="C70">
         <v>45</v>
       </c>
-      <c r="H70">
+      <c r="D70">
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71">
-        <v>70</v>
-      </c>
-      <c r="G71">
+      <c r="C71">
         <v>31</v>
       </c>
-      <c r="H71">
+      <c r="D71">
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72">
-        <v>71</v>
-      </c>
-      <c r="G72">
+      <c r="C72">
         <v>50</v>
       </c>
-      <c r="H72">
+      <c r="D72">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="F73">
-        <v>72</v>
-      </c>
-      <c r="G73">
+      <c r="C73">
         <v>63</v>
       </c>
-      <c r="H73">
+      <c r="D73">
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-      <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74">
-        <v>73</v>
-      </c>
-      <c r="G74">
+      <c r="C74">
         <v>5</v>
       </c>
-      <c r="H74">
+      <c r="D74">
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-      <c r="E75">
-        <v>1</v>
-      </c>
-      <c r="F75">
-        <v>74</v>
-      </c>
-      <c r="G75">
+      <c r="C75">
         <v>18</v>
       </c>
-      <c r="H75">
+      <c r="D75">
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-      <c r="E76">
-        <v>1</v>
-      </c>
-      <c r="F76">
-        <v>75</v>
-      </c>
-      <c r="G76">
+      <c r="C76">
         <v>48</v>
       </c>
-      <c r="H76">
+      <c r="D76">
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-      <c r="E77">
-        <v>1</v>
-      </c>
-      <c r="F77">
-        <v>76</v>
-      </c>
-      <c r="G77">
+      <c r="C77">
         <v>53</v>
       </c>
-      <c r="H77">
+      <c r="D77">
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-      <c r="E78">
-        <v>1</v>
-      </c>
-      <c r="F78">
-        <v>77</v>
-      </c>
-      <c r="G78">
+      <c r="C78">
         <v>38</v>
       </c>
-      <c r="H78">
+      <c r="D78">
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-      <c r="E79">
-        <v>1</v>
-      </c>
-      <c r="F79">
-        <v>78</v>
-      </c>
-      <c r="G79">
+      <c r="C79">
         <v>21</v>
       </c>
-      <c r="H79">
+      <c r="D79">
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-      <c r="E80">
-        <v>1</v>
-      </c>
-      <c r="F80">
-        <v>79</v>
-      </c>
-      <c r="G80">
+      <c r="C80">
         <v>58</v>
       </c>
-      <c r="H80">
+      <c r="D80">
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-      <c r="E81">
-        <v>1</v>
-      </c>
-      <c r="F81">
-        <v>80</v>
-      </c>
-      <c r="G81">
+      <c r="C81">
         <v>22</v>
       </c>
-      <c r="H81">
+      <c r="D81">
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-      <c r="E82">
-        <v>1</v>
-      </c>
-      <c r="F82">
-        <v>81</v>
-      </c>
-      <c r="G82">
+      <c r="C82">
         <v>16</v>
       </c>
-      <c r="H82">
+      <c r="D82">
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-      <c r="E83">
-        <v>1</v>
-      </c>
-      <c r="F83">
-        <v>82</v>
-      </c>
-      <c r="G83">
+      <c r="C83">
         <v>59</v>
       </c>
-      <c r="H83">
+      <c r="D83">
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-      <c r="E84">
-        <v>1</v>
-      </c>
-      <c r="F84">
-        <v>83</v>
-      </c>
-      <c r="G84">
+      <c r="C84">
         <v>40</v>
       </c>
-      <c r="H84">
+      <c r="D84">
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-      <c r="E85">
-        <v>1</v>
-      </c>
-      <c r="F85">
-        <v>84</v>
-      </c>
-      <c r="G85">
+      <c r="C85">
         <v>35</v>
       </c>
-      <c r="H85">
+      <c r="D85">
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-      <c r="F86">
-        <v>85</v>
-      </c>
-      <c r="G86">
+      <c r="C86">
         <v>3</v>
       </c>
-      <c r="H86">
+      <c r="D86">
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-      <c r="E87">
-        <v>1</v>
-      </c>
-      <c r="F87">
-        <v>86</v>
-      </c>
-      <c r="G87">
+      <c r="C87">
         <v>49</v>
       </c>
-      <c r="H87">
+      <c r="D87">
         <v>56</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-      <c r="E88">
-        <v>1</v>
-      </c>
-      <c r="F88">
-        <v>87</v>
-      </c>
-      <c r="G88">
+      <c r="C88">
         <v>27</v>
       </c>
-      <c r="H88">
+      <c r="D88">
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-      <c r="E89">
-        <v>1</v>
-      </c>
-      <c r="F89">
-        <v>88</v>
-      </c>
-      <c r="G89">
+      <c r="C89">
         <v>33</v>
       </c>
-      <c r="H89">
+      <c r="D89">
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-      <c r="E90">
-        <v>1</v>
-      </c>
-      <c r="F90">
-        <v>89</v>
-      </c>
-      <c r="G90">
+      <c r="C90">
         <v>24</v>
       </c>
-      <c r="H90">
+      <c r="D90">
         <v>48</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-      <c r="E91">
-        <v>1</v>
-      </c>
-      <c r="F91">
-        <v>90</v>
-      </c>
-      <c r="G91">
+      <c r="C91">
         <v>61</v>
       </c>
-      <c r="H91">
+      <c r="D91">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-      <c r="E92">
-        <v>1</v>
-      </c>
-      <c r="F92">
-        <v>91</v>
-      </c>
-      <c r="G92">
+      <c r="C92">
         <v>55</v>
       </c>
-      <c r="H92">
+      <c r="D92">
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-      <c r="E93">
-        <v>1</v>
-      </c>
-      <c r="F93">
-        <v>92</v>
-      </c>
-      <c r="G93">
+      <c r="C93">
         <v>52</v>
       </c>
-      <c r="H93">
+      <c r="D93">
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-      <c r="E94">
-        <v>1</v>
-      </c>
-      <c r="F94">
-        <v>93</v>
-      </c>
-      <c r="G94">
+      <c r="C94">
         <v>15</v>
       </c>
-      <c r="H94">
+      <c r="D94">
         <v>55</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-      <c r="E95">
-        <v>1</v>
-      </c>
-      <c r="F95">
-        <v>94</v>
-      </c>
-      <c r="G95">
+      <c r="C95">
         <v>16</v>
       </c>
-      <c r="H95">
+      <c r="D95">
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-      <c r="E96">
-        <v>1</v>
-      </c>
-      <c r="F96">
-        <v>95</v>
-      </c>
-      <c r="G96">
+      <c r="C96">
         <v>28</v>
       </c>
-      <c r="H96">
+      <c r="D96">
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-      <c r="E97">
-        <v>1</v>
-      </c>
-      <c r="F97">
-        <v>96</v>
-      </c>
-      <c r="G97">
+      <c r="C97">
         <v>39</v>
       </c>
-      <c r="H97">
+      <c r="D97">
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-      <c r="F98">
-        <v>97</v>
-      </c>
-      <c r="G98">
+      <c r="C98">
         <v>19</v>
       </c>
-      <c r="H98">
+      <c r="D98">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-      <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99">
-        <v>98</v>
-      </c>
-      <c r="G99">
+      <c r="C99">
         <v>36</v>
       </c>
-      <c r="H99">
+      <c r="D99">
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-      <c r="E100">
-        <v>1</v>
-      </c>
-      <c r="F100">
-        <v>99</v>
-      </c>
-      <c r="G100">
+      <c r="C100">
         <v>7</v>
       </c>
-      <c r="H100">
+      <c r="D100">
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
       </c>
-      <c r="E101">
-        <v>1</v>
-      </c>
-      <c r="F101">
-        <v>100</v>
-      </c>
-      <c r="G101">
+      <c r="C101">
         <v>26</v>
       </c>
-      <c r="H101">
+      <c r="D101">
         <v>30</v>
       </c>
     </row>
@@ -8335,7 +7723,7 @@
         <v>16</v>
       </c>
       <c r="D12">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">

--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F66730A-444C-455F-9893-FDBC24891C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AAB3B4-5255-4205-8399-F71CBD357DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="3" activeTab="4" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="2" activeTab="2" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3585,7 +3585,7 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <v>49</v>

--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AAB3B4-5255-4205-8399-F71CBD357DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17554EB-D9E9-4633-9056-5A8DB0B3D646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="2" activeTab="2" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="7000" yWindow="620" windowWidth="11560" windowHeight="10170" activeTab="1" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1894,10 +1894,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1939,7 +1939,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -2079,7 +2079,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -2510,7 +2510,7 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="D47">
         <v>64</v>
@@ -2776,7 +2776,7 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D66">
         <v>47</v>
@@ -2846,7 +2846,7 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71">
         <v>45</v>
@@ -7709,7 +7709,7 @@
         <v>41</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -7779,7 +7779,7 @@
         <v>58</v>
       </c>
       <c r="D16">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -7793,7 +7793,7 @@
         <v>64</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -7961,7 +7961,7 @@
         <v>23</v>
       </c>
       <c r="D29">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8143,7 +8143,7 @@
         <v>23</v>
       </c>
       <c r="D42">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8199,7 +8199,7 @@
         <v>34</v>
       </c>
       <c r="D46">
-        <v>59</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8213,7 +8213,7 @@
         <v>6</v>
       </c>
       <c r="D47">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8255,7 +8255,7 @@
         <v>59</v>
       </c>
       <c r="D50">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8283,7 +8283,7 @@
         <v>3</v>
       </c>
       <c r="D52">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8633,7 +8633,7 @@
         <v>16</v>
       </c>
       <c r="D77">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8801,7 +8801,7 @@
         <v>6</v>
       </c>
       <c r="D89">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8815,7 +8815,7 @@
         <v>34</v>
       </c>
       <c r="D90">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8829,7 +8829,7 @@
         <v>18</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8843,7 +8843,7 @@
         <v>45</v>
       </c>
       <c r="D92">
-        <v>70</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8857,7 +8857,7 @@
         <v>49</v>
       </c>
       <c r="D93">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8871,7 +8871,7 @@
         <v>3</v>
       </c>
       <c r="D94">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="D95">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8899,7 +8899,7 @@
         <v>40</v>
       </c>
       <c r="D96">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8913,7 +8913,7 @@
         <v>43</v>
       </c>
       <c r="D97">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8927,7 +8927,7 @@
         <v>23</v>
       </c>
       <c r="D98">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8941,7 +8941,7 @@
         <v>69</v>
       </c>
       <c r="D99">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -8955,7 +8955,7 @@
         <v>48</v>
       </c>
       <c r="D100">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">

--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17554EB-D9E9-4633-9056-5A8DB0B3D646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8D962F-78BE-4819-835B-133C2F9D011F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7000" yWindow="620" windowWidth="11560" windowHeight="10170" activeTab="1" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" activeTab="3" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -762,7 +762,7 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>28</v>
@@ -4467,7 +4467,7 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4845,7 +4845,7 @@
         <v>40</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -4873,7 +4873,7 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">

--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8D962F-78BE-4819-835B-133C2F9D011F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBCF67E-997A-467F-86F4-32BF5B891AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" activeTab="3" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
@@ -5657,7 +5657,7 @@
         <v>44</v>
       </c>
       <c r="D68">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">

--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBCF67E-997A-467F-86F4-32BF5B891AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41CF24F-C1B5-49F7-8979-E18C09D86CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" activeTab="3" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="1" activeTab="5" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7037,7 +7037,7 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D65">
         <v>30</v>
@@ -7958,7 +7958,7 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D29">
         <v>22</v>

--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41CF24F-C1B5-49F7-8979-E18C09D86CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E87AC88-AD16-4D15-8F0B-1E8FFB36603F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="1" activeTab="5" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="1" activeTab="4" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6354,7 +6354,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -6407,7 +6407,7 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D20">
         <v>45</v>

--- a/data_VR2.xlsx
+++ b/data_VR2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E87AC88-AD16-4D15-8F0B-1E8FFB36603F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE35262-C1DE-4C38-ADDD-522594CBB691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="520" windowWidth="11560" windowHeight="10170" firstSheet="1" activeTab="4" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="5" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
